--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,49 +680,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129277878</v>
+        <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>92733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607197</v>
+        <v>607496</v>
       </c>
       <c r="R2" t="n">
-        <v>6995987</v>
+        <v>6995921</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277878</t>
+          <t>https://artportalen.se/Sighting/136831198</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129277865</v>
+        <v>129277878</v>
       </c>
       <c r="B3" t="n">
-        <v>92208</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -835,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607464</v>
+        <v>607197</v>
       </c>
       <c r="R3" t="n">
-        <v>6996060</v>
+        <v>6995987</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,16 +902,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277865</t>
+          <t>https://artportalen.se/Sighting/129277878</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129277863</v>
+        <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>79508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,38 +919,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607541</v>
+        <v>607356</v>
       </c>
       <c r="R4" t="n">
-        <v>6995943</v>
+        <v>6996168</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,22 +973,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,69 +1003,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277863</t>
+          <t>https://artportalen.se/Sighting/136831216</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129277870</v>
+        <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>83455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607333</v>
+        <v>607200</v>
       </c>
       <c r="R5" t="n">
-        <v>6995940</v>
+        <v>6995981</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1097,22 +1085,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,66 +1115,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277870</t>
+          <t>https://artportalen.se/Sighting/136831189</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129277880</v>
+        <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>83455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607414</v>
+        <v>607392</v>
       </c>
       <c r="R6" t="n">
-        <v>6995694</v>
+        <v>6995835</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1213,22 +1197,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,27 +1227,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277880</t>
+          <t>https://artportalen.se/Sighting/136831196</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129277866</v>
+        <v>129277865</v>
       </c>
       <c r="B7" t="n">
-        <v>80432</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,21 +1255,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1299,13 +1283,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607465</v>
+        <v>607464</v>
       </c>
       <c r="R7" t="n">
-        <v>6996061</v>
+        <v>6996060</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,16 +1354,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277866</t>
+          <t>https://artportalen.se/Sighting/129277865</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129277868</v>
+        <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>80432</v>
+        <v>92384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,41 +1371,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607360</v>
+        <v>607495</v>
       </c>
       <c r="R8" t="n">
-        <v>6995906</v>
+        <v>6995921</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,22 +1425,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,27 +1455,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277868</t>
+          <t>https://artportalen.se/Sighting/136831197</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129277871</v>
+        <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>80432</v>
+        <v>92384</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,38 +1483,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607336</v>
+        <v>607468</v>
       </c>
       <c r="R9" t="n">
-        <v>6995939</v>
+        <v>6996063</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1561,22 +1537,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,27 +1567,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277871</t>
+          <t>https://artportalen.se/Sighting/136831204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129277875</v>
+        <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>92384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,41 +1595,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607249</v>
+        <v>607412</v>
       </c>
       <c r="R10" t="n">
-        <v>6996018</v>
+        <v>6996067</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,22 +1649,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,27 +1679,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277875</t>
+          <t>https://artportalen.se/Sighting/136831206</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129277876</v>
+        <v>129277863</v>
       </c>
       <c r="B11" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1735,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1763,13 +1735,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607217</v>
+        <v>607541</v>
       </c>
       <c r="R11" t="n">
-        <v>6996002</v>
+        <v>6995943</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1798,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1808,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,16 +1806,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277876</t>
+          <t>https://artportalen.se/Sighting/129277863</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129277879</v>
+        <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>80432</v>
+        <v>92113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1851,41 +1823,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607279</v>
+        <v>607196</v>
       </c>
       <c r="R12" t="n">
-        <v>6995908</v>
+        <v>6996029</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,22 +1877,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,27 +1907,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277879</t>
+          <t>https://artportalen.se/Sighting/136831186</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129277882</v>
+        <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>80432</v>
+        <v>92113</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1967,41 +1935,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607476</v>
+        <v>607498</v>
       </c>
       <c r="R13" t="n">
-        <v>6995692</v>
+        <v>6995923</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2025,22 +1989,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,27 +2019,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277882</t>
+          <t>https://artportalen.se/Sighting/136831199</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129277883</v>
+        <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>80432</v>
+        <v>92113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2083,38 +2047,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607456</v>
+        <v>607413</v>
       </c>
       <c r="R14" t="n">
-        <v>6995702</v>
+        <v>6996067</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2141,22 +2101,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,66 +2131,62 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277883</t>
+          <t>https://artportalen.se/Sighting/136831205</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129277877</v>
+        <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>80461</v>
+        <v>92113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607223</v>
+        <v>607379</v>
       </c>
       <c r="R15" t="n">
-        <v>6996008</v>
+        <v>6996058</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2257,22 +2213,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,66 +2243,62 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277877</t>
+          <t>https://artportalen.se/Sighting/136831208</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129277869</v>
+        <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>80467</v>
+        <v>92113</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607365</v>
+        <v>607360</v>
       </c>
       <c r="R16" t="n">
-        <v>6995907</v>
+        <v>6996116</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2373,22 +2325,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,27 +2355,27 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277869</t>
+          <t>https://artportalen.se/Sighting/136831212</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129277862</v>
+        <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>58057</v>
+        <v>92113</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2431,38 +2383,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103031</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607538</v>
+        <v>607322</v>
       </c>
       <c r="R17" t="n">
-        <v>6995914</v>
+        <v>6996123</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2489,27 +2437,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:02</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>2 individer</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2524,66 +2467,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277862</t>
+          <t>https://artportalen.se/Sighting/136831213</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129277873</v>
+        <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>92113</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607263</v>
+        <v>607338</v>
       </c>
       <c r="R18" t="n">
-        <v>6995980</v>
+        <v>6996141</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2610,27 +2549,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>30 rosetter</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,66 +2579,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129277873</t>
+          <t>https://artportalen.se/Sighting/136831214</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129277874</v>
+        <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>92124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bodviken, Ång</t>
+          <t>Knäsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607269</v>
+        <v>607279</v>
       </c>
       <c r="R19" t="n">
-        <v>6995986</v>
+        <v>6995941</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2731,27 +2661,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>30 rosetter</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,16 +2691,3828 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Amanda Selinder</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831193</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136831200</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92455</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>607497</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6995925</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831200</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136831209</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92076</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>607414</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6996090</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831209</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129277870</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>607333</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6995940</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:46</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277870</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129277880</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>607414</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6995694</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277880</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136831185</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>607194</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6996027</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831185</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136831191</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>607221</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6995967</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:41</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831191</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136831194</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>607268</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6995915</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831194</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136831210</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>607402</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6996128</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831210</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136831215</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>607355</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6996167</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831215</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136831217</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>607342</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6996189</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831217</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136831190</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79500</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>607227</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6995944</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831190</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136831188</v>
+      </c>
+      <c r="B31" t="n">
+        <v>83446</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>607201</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6995981</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831188</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136831187</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83463</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>607191</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6996009</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831187</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136831192</v>
+      </c>
+      <c r="B33" t="n">
+        <v>83463</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>607222</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6995998</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831192</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129277866</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>607465</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6996061</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277866</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129277868</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>607360</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6995906</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277868</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129277871</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>607336</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6995939</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277871</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129277875</v>
+      </c>
+      <c r="B37" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>607249</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6996018</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277875</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129277876</v>
+      </c>
+      <c r="B38" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>607217</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6996002</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277876</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129277879</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>607279</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6995908</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277879</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129277882</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>607476</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6995692</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277882</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129277883</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>607456</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6995702</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277883</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>136831195</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>607256</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6995900</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831195</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>136831202</v>
+      </c>
+      <c r="B43" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>607474</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6995948</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831202</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129277877</v>
+      </c>
+      <c r="B44" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>607223</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6996008</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277877</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129277869</v>
+      </c>
+      <c r="B45" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>607365</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6995907</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277869</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136831211</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>607395</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6996128</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831211</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136831203</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>607435</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6996042</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831203</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>136831201</v>
+      </c>
+      <c r="B48" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>607493</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6995927</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831201</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129277862</v>
+      </c>
+      <c r="B49" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>607538</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6995914</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2 individer</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277862</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>136831207</v>
+      </c>
+      <c r="B50" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Knäsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>607382</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6996063</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136831207</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129277873</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>607263</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6995980</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>30 rosetter</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129277873</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129277874</v>
+      </c>
+      <c r="B52" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Bodviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>607269</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6995986</v>
+      </c>
+      <c r="S52" t="n">
+        <v>5</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>30 rosetter</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Amanda Selinder</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129277874</t>
         </is>
@@ -2801,6 +6538,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92733</v>
+        <v>92735</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79508</v>
+        <v>79512</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83455</v>
+        <v>83459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92455</v>
+        <v>92457</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92735</v>
+        <v>92737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79512</v>
+        <v>79514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83459</v>
+        <v>83461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92126</v>
+        <v>92128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92457</v>
+        <v>92459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92737</v>
+        <v>92738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83461</v>
+        <v>83462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92128</v>
+        <v>92129</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92459</v>
+        <v>92460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79506</v>
+        <v>79507</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92738</v>
+        <v>92744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92129</v>
+        <v>92135</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92460</v>
+        <v>92466</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92744</v>
+        <v>92748</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79515</v>
+        <v>79517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83462</v>
+        <v>83466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92466</v>
+        <v>92470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79507</v>
+        <v>79509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83466</v>
+        <v>83468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92470</v>
+        <v>92472</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79509</v>
+        <v>79512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92750</v>
+        <v>92763</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79520</v>
+        <v>79533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83468</v>
+        <v>83481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92472</v>
+        <v>92485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79512</v>
+        <v>79525</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136831211</v>
       </c>
       <c r="B46" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>136831203</v>
       </c>
       <c r="B47" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>136831201</v>
       </c>
       <c r="B48" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>136831207</v>
       </c>
       <c r="B50" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92763</v>
+        <v>92765</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83481</v>
+        <v>83483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92154</v>
+        <v>92156</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92485</v>
+        <v>92487</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79525</v>
+        <v>79527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136831211</v>
       </c>
       <c r="B46" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>136831203</v>
       </c>
       <c r="B47" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>136831201</v>
       </c>
       <c r="B48" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>136831207</v>
       </c>
       <c r="B50" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -5701,11 +5701,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Knäsjöbäcken, Ång</t>
@@ -5822,16 +5818,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Knäsjöbäcken, Ång</t>
@@ -5948,11 +5936,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Knäsjöbäcken, Ång</t>
@@ -6190,11 +6174,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Knäsjöbäcken, Ång</t>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92765</v>
+        <v>92768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83483</v>
+        <v>83486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92156</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92487</v>
+        <v>92490</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92768</v>
+        <v>92778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83486</v>
+        <v>83496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92159</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92490</v>
+        <v>92500</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79527</v>
+        <v>79537</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136831211</v>
       </c>
       <c r="B46" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136831203</v>
       </c>
       <c r="B47" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>136831201</v>
       </c>
       <c r="B48" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>136831207</v>
       </c>
       <c r="B50" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92778</v>
+        <v>92779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92170</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92500</v>
+        <v>92501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92779</v>
+        <v>92782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83496</v>
+        <v>83499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92170</v>
+        <v>92173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92501</v>
+        <v>92504</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79537</v>
+        <v>79540</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136831211</v>
       </c>
       <c r="B46" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136831203</v>
       </c>
       <c r="B47" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>136831201</v>
       </c>
       <c r="B48" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>136831207</v>
       </c>
       <c r="B50" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92782</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92173</v>
+        <v>92175</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92504</v>
+        <v>92506</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83499</v>
+        <v>83504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92175</v>
+        <v>92180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92506</v>
+        <v>92511</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79540</v>
+        <v>79545</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>136831211</v>
       </c>
       <c r="B46" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>136831203</v>
       </c>
       <c r="B47" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>136831201</v>
       </c>
       <c r="B48" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6144,7 +6144,7 @@
         <v>136831207</v>
       </c>
       <c r="B50" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 35261-2026 artfynd.xlsx
+++ b/artfynd/A 35261-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136831198</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92801</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136831216</v>
       </c>
       <c r="B4" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         <v>136831189</v>
       </c>
       <c r="B5" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136831196</v>
       </c>
       <c r="B6" t="n">
-        <v>83504</v>
+        <v>83515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>136831197</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>136831204</v>
       </c>
       <c r="B9" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>136831206</v>
       </c>
       <c r="B10" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1815,7 +1815,7 @@
         <v>136831186</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>136831199</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>136831205</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>136831208</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>136831212</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>136831213</v>
       </c>
       <c r="B17" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>136831214</v>
       </c>
       <c r="B18" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>136831193</v>
       </c>
       <c r="B19" t="n">
-        <v>92180</v>
+        <v>92192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>136831200</v>
       </c>
       <c r="B20" t="n">
-        <v>92511</v>
+        <v>92523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>136831209</v>
       </c>
       <c r="B21" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>136831185</v>
       </c>
       <c r="B24" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3279,7 +3279,7 @@
         <v>136831191</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3391,7 +3391,7 @@
         <v>136831194</v>
       </c>
       <c r="B26" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>136831210</v>
       </c>
       <c r="B27" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>136831215</v>
       </c>
       <c r="B28" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3727,7 +3727,7 @@
         <v>136831217</v>
       </c>
       <c r="B29" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>136831190</v>
       </c>
       <c r="B30" t="n">
-        <v>79545</v>
+        <v>79556</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>136831188</v>
       </c>
       <c r="B31" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>136831187</v>
       </c>
       <c r="B32" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>136831192</v>
       </c>
       <c r="B33" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>136831195</v>
       </c>
       <c r="B42" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5327,7 +5327,7 @@
         <v>136831202</v>
       </c>
       <c r="B43" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
